--- a/outputs/rbac-feature-matrix-20260705/terumbu-rbac-feature-matrix.xlsx
+++ b/outputs/rbac-feature-matrix-20260705/terumbu-rbac-feature-matrix.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R68ae84ad8af24814"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RBAC Matrix" sheetId="2" r:id="R36165b0aebb14c9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Role Definitions" sheetId="3" r:id="R2b0c622b8ee6455b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="4" r:id="Rf351b388b82d495a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd6e7c1c4738740ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RBAC Matrix" sheetId="2" r:id="Rb2e4f33118aa4d14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Role Definitions" sheetId="3" r:id="R60466df8f4d142a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="4" r:id="Rcc33703cf20e49dc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -725,8 +725,9 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="6" t="str">
-        <x:v>Generated 2026-07-05. Based on repository references, role guides, route guards, and server actions.</x:v>
-      </x:c>
+        <x:v>Updated 2026-07-11 after RBAC/admin-user, review moderation, billing lifecycle, and expedition booking lifecycle hardening.</x:v>
+      </x:c>
+      <x:c r="B2"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="36" t="str">
@@ -761,8 +762,7 @@
         <x:v>Implemented</x:v>
       </x:c>
       <x:c r="B8" s="39" t="n">
-        <x:f>COUNTIF('RBAC Matrix'!$N$5:$N$39,"Implemented")</x:f>
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -770,8 +770,7 @@
         <x:v>Mostly implemented</x:v>
       </x:c>
       <x:c r="B9" s="39" t="n">
-        <x:f>COUNTIF('RBAC Matrix'!$N$5:$N$39,"Mostly implemented")</x:f>
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -779,8 +778,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="B10" s="39" t="n">
-        <x:f>COUNTIF('RBAC Matrix'!$N$5:$N$39,"Partial")</x:f>
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -788,7 +786,6 @@
         <x:v>Not implemented</x:v>
       </x:c>
       <x:c r="B11" s="39" t="n">
-        <x:f>COUNTIF('RBAC Matrix'!$N$5:$N$39,"Not implemented")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -807,7 +804,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B14" s="39" t="str">
-        <x:v>Corporate access is account-scoped through corporate_permissions; the top-level corporate_admin role is only part of the access story.</x:v>
+        <x:v>Corporate access is account-scoped through corporate_permissions and now enforced with shared corporate dashboard access guards plus centralized sub-role capabilities.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -815,7 +812,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B15" s="39" t="str">
-        <x:v>Admin and partner route groups are strongly guarded by requireRole, while dashboard routes are available to every authenticated role for own data.</x:v>
+        <x:v>Partner owner/manager/contributor/viewer permissions are now enforced in server actions and reflected in partner UI capabilities.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -823,7 +820,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B16" s="39" t="str">
-        <x:v>Corporate report workflow is the most granular implemented permission split; wider corporate/partner CRUD permissions need hardening.</x:v>
+        <x:v>Admin user management now covers account creation, profile edits, password/session controls, global roles, partner memberships, corporate permissions, and audit logs.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -831,7 +828,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B17" s="45" t="str">
-        <x:v>The E2E reference expects explicit forbidden redirects, but requireRole currently redirects to the user's default authenticated path.</x:v>
+        <x:v>Unauthorized signed-in users now land on an explicit /forbidden page with the requested protected path preserved in next.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1144,16 +1141,16 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="O8" s="54" t="str">
-        <x:v>Recurring billing scheduler/provider integration, durable subscription charge collection, provider-backed payment methods, and email preferences are not production-grade.</x:v>
+        <x:v>Recurring billing scheduler/provider integration, durable subscription charge collection, and email preferences remain; subscription method switching and active-method archive guards are now implemented.</x:v>
       </x:c>
       <x:c r="P8" s="54" t="str">
-        <x:v>Billing actions use requireUser; admin reconciliation is separate from user self-service.</x:v>
+        <x:v>Billing actions use requireUser; admin reconciliation is separate from user self-service; active subscriptions cannot lose their payment method through archive.</x:v>
       </x:c>
       <x:c r="Q8" s="54" t="str">
         <x:v>references/2. review-campaign-detail.md; references/3. review-user-dashboard.md</x:v>
       </x:c>
       <x:c r="R8" s="39" t="str">
-        <x:v>src/lib/billing-actions.ts; src/lib/checkout-actions.ts; src/lib/payment-workflows.ts</x:v>
+        <x:v>src/lib/billing-lifecycle.ts; src/lib/billing-actions.ts; src/lib/checkout-actions.ts; src/lib/payment-workflows.ts; src/app/dashboard/donations/page.tsx; tests/billing-lifecycle.test.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1368,16 +1365,16 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="O12" s="54" t="str">
-        <x:v>Full five-step checkout, add-ons, waitlist, private departure, minimum-participant automation, and operator cancellation workflows remain.</x:v>
+        <x:v>Full five-step checkout, add-ons, waitlist interest capture, private departure request flow, and operator cancellation workflow remain; booking now has centralized departure availability guards and automatic full/open seat-state transitions.</x:v>
       </x:c>
       <x:c r="P12" s="54" t="str">
-        <x:v>Booking backend persists booking/payment records; dashboard access is authenticated.</x:v>
+        <x:v>Checkout and retry payment re-check departure status/capacity; dashboard shows availability errors; admin sees minimum/availability messaging.</x:v>
       </x:c>
       <x:c r="Q12" s="54" t="str">
         <x:v>references/4. review-trip-detail.md; references/8. end-to-end-test-case.md</x:v>
       </x:c>
       <x:c r="R12" s="39" t="str">
-        <x:v>src/lib/checkout-actions.ts; src/app/checkout/expedition/page.tsx; src/app/dashboard/expeditions/page.tsx</x:v>
+        <x:v>src/lib/expedition-booking-lifecycle.ts; src/lib/checkout-actions.ts; src/lib/payment-workflows.ts; src/lib/billing-actions.ts; src/lib/queries.ts; src/app/checkout/expedition/page.tsx; src/app/dashboard/expeditions/page.tsx; tests/expedition-booking-lifecycle.test.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1391,7 +1388,7 @@
         <x:v>/dashboard/expeditions</x:v>
       </x:c>
       <x:c r="D13" s="54" t="str">
-        <x:v>First version</x:v>
+        <x:v>Moderated workflow</x:v>
       </x:c>
       <x:c r="E13" s="83" t="str">
         <x:v>No</x:v>
@@ -1421,19 +1418,19 @@
         <x:v>Own submit</x:v>
       </x:c>
       <x:c r="N13" s="75" t="str">
-        <x:v>Partial</x:v>
+        <x:v>Mostly implemented</x:v>
       </x:c>
       <x:c r="O13" s="54" t="str">
-        <x:v>Moderation status, review media, review filters, and richer public review workflows remain.</x:v>
+        <x:v>Review media uploads, rating filters, and richer public review workflows remain.</x:v>
       </x:c>
       <x:c r="P13" s="54" t="str">
-        <x:v>Server action requires a logged-in user and should be treated as an owner/participant workflow.</x:v>
+        <x:v>Completed-user reviews now submit as pending, can be resubmitted, and require admin approve/reject moderation before public visibility.</x:v>
       </x:c>
       <x:c r="Q13" s="54" t="str">
         <x:v>references/4. review-trip-detail.md</x:v>
       </x:c>
       <x:c r="R13" s="39" t="str">
-        <x:v>src/lib/expedition-review-actions.ts; src/app/dashboard/expeditions/page.tsx</x:v>
+        <x:v>src/lib/expedition-reviews.ts; src/lib/expedition-review-actions.ts; src/app/dashboard/expeditions/page.tsx; src/app/admin/expeditions/[expeditionId]/page.tsx; src/lib/queries.ts; tests/expedition-reviews.test.ts; drizzle/0012_expedition_review_moderation.sql</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1648,16 +1645,16 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="O17" s="54" t="str">
-        <x:v>Provider-backed payment-method management, real refund provider flow, coral monitoring history, and evidence/media stream remain.</x:v>
+        <x:v>Real provider refund settlement, coral monitoring history, and evidence/media stream remain; payment-method lifecycle guards and subscription reassignment are now implemented.</x:v>
       </x:c>
       <x:c r="P17" s="54" t="str">
-        <x:v>User requests refunds; admin reconciles payments in admin workflows.</x:v>
+        <x:v>User requests refunds; admin reconciles payments in admin workflows; dashboard prevents archiving methods that back active monthly giving.</x:v>
       </x:c>
       <x:c r="Q17" s="54" t="str">
         <x:v>references/3. review-user-dashboard.md; references/5. review-impact-passport.md</x:v>
       </x:c>
       <x:c r="R17" s="39" t="str">
-        <x:v>src/app/dashboard/donations/page.tsx; src/lib/billing-actions.ts; src/app/dashboard/corals/[code]/page.tsx</x:v>
+        <x:v>src/app/dashboard/donations/page.tsx; src/lib/billing-lifecycle.ts; src/lib/billing-actions.ts; src/app/dashboard/corals/[code]/page.tsx; tests/billing-lifecycle.test.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1869,19 +1866,19 @@
         <x:v>Allow</x:v>
       </x:c>
       <x:c r="N21" s="67" t="str">
-        <x:v>Mostly implemented</x:v>
+        <x:v>Implemented</x:v>
       </x:c>
       <x:c r="O21" s="54" t="str">
-        <x:v>Granular partner permissions by owner/manager/contributor/viewer still need deeper enforcement.</x:v>
+        <x:v>No major partner shell or route-guard gap remains; invitation lifecycle, partner member audit history, and deeper product workflows remain by area.</x:v>
       </x:c>
       <x:c r="P21" s="54" t="str">
-        <x:v>Partner layout allows partner and admin roles.</x:v>
+        <x:v>Partner layout allows partner/admin; active organization membership roles now feed owner/manager/contributor/viewer capability checks.</x:v>
       </x:c>
       <x:c r="Q21" s="54" t="str">
         <x:v>docs/user-guides/partner.md; references/8. end-to-end-test-case.md</x:v>
       </x:c>
       <x:c r="R21" s="39" t="str">
-        <x:v>src/app/partner/layout.tsx; src/app/partner/page.tsx; src/components/partner-shell.tsx</x:v>
+        <x:v>src/app/partner/layout.tsx; src/app/partner/page.tsx; src/components/partner-shell.tsx; src/lib/partner-permissions.ts; src/lib/queries.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1919,7 +1916,7 @@
         <x:v>Forbidden</x:v>
       </x:c>
       <x:c r="L22" s="71" t="str">
-        <x:v>Manage own org</x:v>
+        <x:v>Owner/manager manage own org; contributor/viewer read-limited</x:v>
       </x:c>
       <x:c r="M22" s="71" t="str">
         <x:v>Manage</x:v>
@@ -1928,16 +1925,16 @@
         <x:v>Mostly implemented</x:v>
       </x:c>
       <x:c r="O22" s="54" t="str">
-        <x:v>Partner member role granularity, publish approval workflow, richer media/budget/timeline tables, and audit history remain.</x:v>
+        <x:v>Publish approval workflow, richer media/budget/timeline tables, and audit history remain; partner member role granularity is now enforced.</x:v>
       </x:c>
       <x:c r="P22" s="54" t="str">
-        <x:v>Partner campaigns are limited to draft/review statuses and organization access checks.</x:v>
+        <x:v>Server actions require campaign:create/update/delete capabilities; owner can delete, manager can create/update, contributor/viewer are restricted.</x:v>
       </x:c>
       <x:c r="Q22" s="54" t="str">
         <x:v>docs/user-guides/partner.md; references/8. end-to-end-test-case.md</x:v>
       </x:c>
       <x:c r="R22" s="39" t="str">
-        <x:v>src/lib/portal-actions.ts; src/components/partner-portal-ui.tsx; src/app/partner/campaigns/page.tsx</x:v>
+        <x:v>src/lib/partner-permissions.ts; src/lib/portal-actions.ts; src/components/partner-portal-ui.tsx; src/app/partner/campaigns/page.tsx</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1975,7 +1972,7 @@
         <x:v>Forbidden</x:v>
       </x:c>
       <x:c r="L23" s="71" t="str">
-        <x:v>Submit own org</x:v>
+        <x:v>Owner/manager/contributor submit or revise; viewer read-limited</x:v>
       </x:c>
       <x:c r="M23" s="71" t="str">
         <x:v>Submit/review</x:v>
@@ -1984,16 +1981,16 @@
         <x:v>Mostly implemented</x:v>
       </x:c>
       <x:c r="O23" s="54" t="str">
-        <x:v>Evidence upload/provider workflow, partner-specific review queues, and role-level submit/review separation need hardening.</x:v>
+        <x:v>Evidence upload/provider workflow and partner-specific review queues remain; role-level activity/evidence create/revise checks are now enforced.</x:v>
       </x:c>
       <x:c r="P23" s="54" t="str">
-        <x:v>Admin verification is a separate admin-only workflow.</x:v>
+        <x:v>activity:create and evidence:revise capabilities gate forms and server actions; admin verification remains admin-only.</x:v>
       </x:c>
       <x:c r="Q23" s="54" t="str">
         <x:v>docs/user-guides/partner.md; references/8. end-to-end-test-case.md</x:v>
       </x:c>
       <x:c r="R23" s="39" t="str">
-        <x:v>src/lib/portal-actions.ts; src/app/partner/evidence/submit/page.tsx; src/app/admin/campaigns/evidence/page.tsx</x:v>
+        <x:v>src/lib/partner-permissions.ts; src/lib/portal-actions.ts; src/app/partner/activity/page.tsx; src/app/partner/evidence/page.tsx</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -2031,7 +2028,7 @@
         <x:v>Forbidden</x:v>
       </x:c>
       <x:c r="L24" s="71" t="str">
-        <x:v>Manage linked campaigns</x:v>
+        <x:v>Owner/manager manage; contributor/viewer read-limited</x:v>
       </x:c>
       <x:c r="M24" s="71" t="str">
         <x:v>Manage</x:v>
@@ -2040,16 +2037,16 @@
         <x:v>Mostly implemented</x:v>
       </x:c>
       <x:c r="O24" s="54" t="str">
-        <x:v>Move metadata into dedicated tables; add waitlist/private-trip workflows, media library, review moderation, and availability analytics.</x:v>
+        <x:v>Move metadata into dedicated tables; add waitlist/private-trip workflows, media library, partner review insights, and availability analytics. Role-level expedition management is now enforced.</x:v>
       </x:c>
       <x:c r="P24" s="54" t="str">
-        <x:v>Partner can manage public trip-detail metadata for expeditions tied to their campaigns.</x:v>
+        <x:v>expedition:manage capability gates partner trip detail and departure forms.</x:v>
       </x:c>
       <x:c r="Q24" s="54" t="str">
         <x:v>references/4. review-trip-detail.md; docs/user-guides/partner.md</x:v>
       </x:c>
       <x:c r="R24" s="39" t="str">
-        <x:v>src/app/partner/expeditions/page.tsx; src/components/partner-expedition-editor.tsx; src/lib/portal-actions.ts</x:v>
+        <x:v>src/lib/partner-permissions.ts; src/lib/portal-actions.ts; src/components/partner-expedition-editor.tsx; src/app/partner/expeditions/page.tsx</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -2208,16 +2205,16 @@
         <x:v>Mostly implemented</x:v>
       </x:c>
       <x:c r="O27" s="54" t="str">
-        <x:v>Normalize expedition metadata, add add-ons, waitlists, private departures, operator cancellation, and review moderation.</x:v>
+        <x:v>Normalize expedition metadata, add add-ons, waitlist/private request workflows, operator cancellation, and review media/filter tooling.</x:v>
       </x:c>
       <x:c r="P27" s="54" t="str">
-        <x:v>Admin can create/update/delete expeditions and departures.</x:v>
+        <x:v>Admin can create/update/delete expeditions/departures, moderate participant reviews, and inspect lifecycle availability/minimum participant messaging.</x:v>
       </x:c>
       <x:c r="Q27" s="54" t="str">
         <x:v>references/4. review-trip-detail.md; DEVELOPMENT_PLAN.md</x:v>
       </x:c>
       <x:c r="R27" s="39" t="str">
-        <x:v>src/app/admin/expeditions/page.tsx; src/app/admin/expeditions/[expeditionId]/page.tsx; src/lib/portal-actions.ts</x:v>
+        <x:v>src/app/admin/expeditions/page.tsx; src/app/admin/expeditions/[expeditionId]/page.tsx; src/lib/portal-actions.ts; src/lib/expedition-review-actions.ts; src/lib/expedition-booking-lifecycle.ts; src/lib/queries.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2264,16 +2261,16 @@
         <x:v>Mostly implemented</x:v>
       </x:c>
       <x:c r="O28" s="54" t="str">
-        <x:v>Granular partner member permissions, invitation lifecycle, immutable verification documents, and broader audit trail remain.</x:v>
+        <x:v>Invitation lifecycle, immutable verification documents, and broader audit trail remain; partner member role model is now enforced in the partner portal.</x:v>
       </x:c>
       <x:c r="P28" s="54" t="str">
-        <x:v>Admin manages partner profile, verification level, and organization users.</x:v>
+        <x:v>Admin manages partner profile, verification level, and organization users; partner portal capabilities enforce those member roles.</x:v>
       </x:c>
       <x:c r="Q28" s="54" t="str">
         <x:v>DEVELOPMENT_PLAN.md; docs/user-guides/admin.md</x:v>
       </x:c>
       <x:c r="R28" s="39" t="str">
-        <x:v>src/app/admin/partners/[partnerId]/page.tsx; src/lib/portal-actions.ts; src/db/schema.ts</x:v>
+        <x:v>src/app/admin/partners/[partnerId]/page.tsx; src/lib/portal-actions.ts; src/lib/partner-permissions.ts; src/db/schema.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2432,16 +2429,16 @@
         <x:v>Mostly implemented</x:v>
       </x:c>
       <x:c r="O31" s="54" t="str">
-        <x:v>Role assignment UI, admin-created user flows beyond partner users, report filters, durable export storage, and richer audit querying remain.</x:v>
+        <x:v>Report filters, durable export storage, and richer audit querying remain; full admin-created user/global/scoped role management is implemented.</x:v>
       </x:c>
       <x:c r="P31" s="54" t="str">
-        <x:v>Admin reports page sees corporate export artifacts without granting corporate workspace access.</x:v>
+        <x:v>Admin users now manage accounts, credentials, sessions, global roles, partner org memberships, corporate account permissions, and audit logs.</x:v>
       </x:c>
       <x:c r="Q31" s="54" t="str">
         <x:v>docs/user-guides/admin.md; references/8. end-to-end-test-case.md</x:v>
       </x:c>
       <x:c r="R31" s="39" t="str">
-        <x:v>src/app/admin/reports/page.tsx; src/app/admin/users/page.tsx; src/app/admin/audit/page.tsx</x:v>
+        <x:v>src/app/admin/reports/page.tsx; src/app/admin/users/page.tsx; src/app/admin/audit/page.tsx; src/lib/admin-user-actions.ts; src/lib/admin-user-management.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -2488,16 +2485,16 @@
         <x:v>Mostly implemented</x:v>
       </x:c>
       <x:c r="O32" s="54" t="str">
-        <x:v>Many workflows are derived/presentational; durable approval, benchmark, event, integration, notification, and passport entities remain.</x:v>
+        <x:v>Many workflows are derived/presentational; durable approval, benchmark, event, integration, notification, and passport entities remain. Corporate access guardrails are implemented.</x:v>
       </x:c>
       <x:c r="P32" s="54" t="str">
-        <x:v>Corporate access is based on corporate_permissions; top-level corporate_admin alone is not the only access signal.</x:v>
+        <x:v>Corporate workspace pages now require account-scoped corporate dashboard data instead of showing empty states to unauthorized accounts.</x:v>
       </x:c>
       <x:c r="Q32" s="54" t="str">
         <x:v>references/6. review-corporate-dashboard.md; DEVELOPMENT_PLAN.md</x:v>
       </x:c>
       <x:c r="R32" s="39" t="str">
-        <x:v>src/app/corporate/layout.tsx; src/app/corporate/page.tsx; src/lib/queries.ts</x:v>
+        <x:v>src/app/corporate/layout.tsx; src/app/corporate/page.tsx; src/lib/corporate-access.ts; src/lib/queries.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -2520,10 +2517,10 @@
         <x:v>No corporate program</x:v>
       </x:c>
       <x:c r="G33" s="71" t="str">
-        <x:v>View/manage</x:v>
+        <x:v>Manage programs/projects/funding</x:v>
       </x:c>
       <x:c r="H33" s="71" t="str">
-        <x:v>Review finance</x:v>
+        <x:v>Manage funding / review finance</x:v>
       </x:c>
       <x:c r="I33" s="71" t="str">
         <x:v>View</x:v>
@@ -2544,16 +2541,16 @@
         <x:v>Mostly implemented</x:v>
       </x:c>
       <x:c r="O33" s="54" t="str">
-        <x:v>Actual approval mutations, saved views, filters, variance explanations, attachments, and finance export controls remain.</x:v>
+        <x:v>Saved views, filters, variance explanations, attachments, and finance export controls remain; project/funding mutations are now capability-gated.</x:v>
       </x:c>
       <x:c r="P33" s="54" t="str">
-        <x:v>Program context is loaded from corporate_permissions joined to accounts/programs.</x:v>
+        <x:v>Program/project/funding actions and forms use centralized corporate capabilities.</x:v>
       </x:c>
       <x:c r="Q33" s="54" t="str">
         <x:v>references/6. review-corporate-dashboard.md; README.md</x:v>
       </x:c>
       <x:c r="R33" s="39" t="str">
-        <x:v>src/app/corporate/projects/page.tsx; src/app/corporate/funding/page.tsx; src/db/schema.ts</x:v>
+        <x:v>src/lib/corporate-permissions.ts; src/lib/corporate-actions.ts; src/app/corporate/projects/page.tsx; src/app/corporate/funding/page.tsx</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -2576,10 +2573,10 @@
         <x:v>No corporate program</x:v>
       </x:c>
       <x:c r="G34" s="71" t="str">
-        <x:v>Review/view</x:v>
+        <x:v>Review/update</x:v>
       </x:c>
       <x:c r="H34" s="71" t="str">
-        <x:v>View finance evidence</x:v>
+        <x:v>Review/update</x:v>
       </x:c>
       <x:c r="I34" s="71" t="str">
         <x:v>View approved</x:v>
@@ -2588,7 +2585,7 @@
         <x:v>View participation evidence</x:v>
       </x:c>
       <x:c r="K34" s="54" t="str">
-        <x:v>Audit evidence</x:v>
+        <x:v>Audit/read</x:v>
       </x:c>
       <x:c r="L34" s="71" t="str">
         <x:v>No corporate program</x:v>
@@ -2600,16 +2597,16 @@
         <x:v>Mostly implemented</x:v>
       </x:c>
       <x:c r="O34" s="54" t="str">
-        <x:v>Actual reviewer mutations, clarification workflow, reviewer assignment, and immutable audit/version history remain.</x:v>
+        <x:v>Clarification workflow, reviewer assignment, and immutable audit/version history remain; evidence status mutation is hardened by sub-role.</x:v>
       </x:c>
       <x:c r="P34" s="54" t="str">
-        <x:v>Corporate evidence is visible inside program context; platform evidence verification remains admin-only.</x:v>
+        <x:v>Managers and finance reviewers can update evidence status; auditors can inspect evidence and audit history without mutation controls.</x:v>
       </x:c>
       <x:c r="Q34" s="54" t="str">
         <x:v>references/6. review-corporate-dashboard.md</x:v>
       </x:c>
       <x:c r="R34" s="39" t="str">
-        <x:v>src/app/corporate/evidence/page.tsx; src/lib/queries.ts; src/db/schema.ts</x:v>
+        <x:v>src/lib/corporate-permissions.ts; src/lib/corporate-actions.ts; src/app/corporate/evidence/page.tsx; src/lib/queries.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -2656,16 +2653,16 @@
         <x:v>Mostly implemented</x:v>
       </x:c>
       <x:c r="O35" s="54" t="str">
-        <x:v>Production PDF/XLSX outputs, durable object storage, scheduled generation, audit/version history, and broader corporate permission enforcement remain.</x:v>
+        <x:v>Production PDF/XLSX outputs, durable object storage, scheduled generation, and audit/version history remain.</x:v>
       </x:c>
       <x:c r="P35" s="54" t="str">
-        <x:v>Potential nuance: UI reportCapabilities and action roleCapabilities differ for esg_manager approval; program.manage currently has full report workflow.</x:v>
+        <x:v>Report capabilities and actions now share centralized corporate capability logic; managers generate/submit/publish, finance approves/previews, viewers preview.</x:v>
       </x:c>
       <x:c r="Q35" s="54" t="str">
         <x:v>references/6. review-corporate-dashboard.md; TERUMBU_IMPLEMENTATION_PLAN_COMPARISON.md</x:v>
       </x:c>
       <x:c r="R35" s="39" t="str">
-        <x:v>src/app/corporate/reports/page.tsx; src/lib/corporate-actions.ts; src/app/admin/reports/page.tsx</x:v>
+        <x:v>src/lib/corporate-permissions.ts; src/lib/corporate-actions.ts; src/app/corporate/reports/page.tsx; src/app/admin/reports/page.tsx</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -2753,10 +2750,10 @@
         <x:v>View summary</x:v>
       </x:c>
       <x:c r="J37" s="71" t="str">
-        <x:v>Manage intended</x:v>
+        <x:v>Manage allowed employee roles</x:v>
       </x:c>
       <x:c r="K37" s="54" t="str">
-        <x:v>Audit</x:v>
+        <x:v>Audit/read</x:v>
       </x:c>
       <x:c r="L37" s="71" t="str">
         <x:v>No corporate program</x:v>
@@ -2765,19 +2762,19 @@
         <x:v>No program unless granted</x:v>
       </x:c>
       <x:c r="N37" s="75" t="str">
-        <x:v>Partial</x:v>
+        <x:v>Mostly implemented</x:v>
       </x:c>
       <x:c r="O37" s="54" t="str">
-        <x:v>Event creation/check-in/waitlist/reminders, eligibility workflows, durable challenge rules, attendance exports, and HR sync remain.</x:v>
+        <x:v>Event creation/check-in/waitlist/reminders, eligibility workflows, durable challenge rules, attendance exports, and HR sync remain; employee invite/update and role escalation controls are implemented.</x:v>
       </x:c>
       <x:c r="P37" s="54" t="str">
-        <x:v>Employee Engagement Manager is documented in the role matrix, but most mutations are still future work.</x:v>
+        <x:v>Employee Engagement can assign member, report_viewer, and employee_engagement only; program managers can assign all corporate employee roles.</x:v>
       </x:c>
       <x:c r="Q37" s="54" t="str">
         <x:v>references/6. review-corporate-dashboard.md; src/lib/queries.ts roleCapabilities</x:v>
       </x:c>
       <x:c r="R37" s="39" t="str">
-        <x:v>src/app/corporate/employees/page.tsx; src/app/corporate/settings/page.tsx; src/lib/queries.ts</x:v>
+        <x:v>src/lib/corporate-permissions.ts; src/lib/corporate-actions.ts; src/app/corporate/employees/page.tsx; tests/corporate-permissions.test.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -2800,19 +2797,19 @@
         <x:v>No corporate program</x:v>
       </x:c>
       <x:c r="G38" s="71" t="str">
-        <x:v>View/manage intended</x:v>
+        <x:v>Manage settings</x:v>
       </x:c>
       <x:c r="H38" s="71" t="str">
-        <x:v>View finance settings</x:v>
+        <x:v>View/read-only</x:v>
       </x:c>
       <x:c r="I38" s="71" t="str">
         <x:v>View</x:v>
       </x:c>
       <x:c r="J38" s="71" t="str">
-        <x:v>View</x:v>
+        <x:v>View/read-only</x:v>
       </x:c>
       <x:c r="K38" s="54" t="str">
-        <x:v>Audit</x:v>
+        <x:v>Audit/read</x:v>
       </x:c>
       <x:c r="L38" s="71" t="str">
         <x:v>No corporate program</x:v>
@@ -2821,19 +2818,19 @@
         <x:v>No program unless granted</x:v>
       </x:c>
       <x:c r="N38" s="75" t="str">
-        <x:v>Partial</x:v>
+        <x:v>Mostly implemented</x:v>
       </x:c>
       <x:c r="O38" s="54" t="str">
-        <x:v>Invite/change-role/suspend mutations, SSO/MFA/domain/session enforcement, real connector setup, and retention policy are not implemented.</x:v>
+        <x:v>SSO/MFA/domain/session enforcement and real connector setup remain; integration/security settings persist and are capability-gated.</x:v>
       </x:c>
       <x:c r="P38" s="54" t="str">
-        <x:v>Settings currently explains role capabilities and security readiness more than it mutates access.</x:v>
+        <x:v>Corporate settings mutation now requires canManageSettings; admin user management covers global and scoped access assignment outside the corporate workspace.</x:v>
       </x:c>
       <x:c r="Q38" s="54" t="str">
         <x:v>references/6. review-corporate-dashboard.md; src/app/corporate/settings/page.tsx</x:v>
       </x:c>
       <x:c r="R38" s="39" t="str">
-        <x:v>src/app/corporate/settings/page.tsx; src/lib/queries.ts; src/db/schema.ts</x:v>
+        <x:v>src/lib/corporate-permissions.ts; src/lib/corporate-actions.ts; src/app/corporate/settings/page.tsx; src/lib/admin-user-actions.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2877,19 +2874,19 @@
         <x:v>Admin default</x:v>
       </x:c>
       <x:c r="N39" s="91" t="str">
-        <x:v>Mostly implemented</x:v>
+        <x:v>Implemented</x:v>
       </x:c>
       <x:c r="O39" s="55" t="str">
-        <x:v>E2E reference expects forbidden redirects with ?error=forbidden, while requireRole redirects users to their default authenticated path without that explicit error.</x:v>
+        <x:v>No known explicit forbidden redirect gap remains; remaining work is automated browser E2E coverage and any desired ?error=forbidden convention alignment.</x:v>
       </x:c>
       <x:c r="P39" s="55" t="str">
-        <x:v>Roles are user, corporate_admin, partner, admin; corporate_permissions add account-scoped corporate access.</x:v>
+        <x:v>requireRole redirects unauthorized signed-in users to /forbidden?next=...; login redirects are still used for unauthenticated users.</x:v>
       </x:c>
       <x:c r="Q39" s="55" t="str">
         <x:v>references/8. end-to-end-test-case.md; docs/user-guides/*.md; README.md</x:v>
       </x:c>
       <x:c r="R39" s="45" t="str">
-        <x:v>src/lib/auth.ts; src/lib/account-destinations.ts; src/app/admin/layout.tsx; src/app/partner/layout.tsx; src/app/corporate/layout.tsx</x:v>
+        <x:v>src/lib/auth.ts; src/lib/account-destinations.ts; src/app/forbidden/page.tsx; tests/account-destinations.test.ts</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2996,10 +2993,10 @@
         <x:v>/corporate</x:v>
       </x:c>
       <x:c r="E7" s="54" t="str">
-        <x:v>Can access corporate workspace. program.manage seed has full report flow; esg_manager is documented for generate/submit/publish.</x:v>
+        <x:v>Can access corporate workspace. Program managers can manage settings, projects, employees, reports, and programs through capability-gated actions.</x:v>
       </x:c>
       <x:c r="F7" s="39" t="str">
-        <x:v>docs/user-guides/corporate-admin.md; src/lib/queries.ts; src/lib/corporate-actions.ts</x:v>
+        <x:v>docs/user-guides/corporate-admin.md; src/lib/corporate-permissions.ts; src/lib/corporate-actions.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3016,10 +3013,10 @@
         <x:v>/corporate</x:v>
       </x:c>
       <x:c r="E8" s="54" t="str">
-        <x:v>Review funding/utilization and approve/preview reports.</x:v>
+        <x:v>Review funding/utilization, update finance/evidence review status, and approve/preview reports without workspace settings or project-admin powers.</x:v>
       </x:c>
       <x:c r="F8" s="39" t="str">
-        <x:v>src/lib/queries.ts; src/lib/corporate-actions.ts</x:v>
+        <x:v>src/lib/corporate-permissions.ts; src/lib/corporate-actions.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3036,10 +3033,10 @@
         <x:v>/corporate</x:v>
       </x:c>
       <x:c r="E9" s="54" t="str">
-        <x:v>View KPIs, portfolio progress, major risks, and approved/public report outputs.</x:v>
+        <x:v>View KPIs, portfolio progress, major risks, and approved/public report outputs without mutation controls.</x:v>
       </x:c>
       <x:c r="F9" s="39" t="str">
-        <x:v>src/lib/queries.ts</x:v>
+        <x:v>src/lib/corporate-permissions.ts; src/lib/queries.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3056,10 +3053,10 @@
         <x:v>/corporate/employees</x:v>
       </x:c>
       <x:c r="E10" s="54" t="str">
-        <x:v>Intended for events, employee participation, challenges, and attendance exports. Mutations remain shallow.</x:v>
+        <x:v>Manage employee roster for non-privileged employee roles and review employee participation programs.</x:v>
       </x:c>
       <x:c r="F10" s="39" t="str">
-        <x:v>src/lib/queries.ts; references/6. review-corporate-dashboard.md</x:v>
+        <x:v>src/lib/corporate-permissions.ts; src/app/corporate/employees/page.tsx</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3076,10 +3073,10 @@
         <x:v>/corporate/evidence</x:v>
       </x:c>
       <x:c r="E11" s="54" t="str">
-        <x:v>Read approved evidence, financial summaries, methodology, and report previews.</x:v>
+        <x:v>Read evidence, audit history, methodology, and report previews without changing evidence status.</x:v>
       </x:c>
       <x:c r="F11" s="39" t="str">
-        <x:v>src/lib/queries.ts; src/lib/corporate-actions.ts</x:v>
+        <x:v>src/lib/corporate-permissions.ts; src/app/corporate/evidence/page.tsx</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3096,10 +3093,10 @@
         <x:v>/partner</x:v>
       </x:c>
       <x:c r="E12" s="54" t="str">
-        <x:v>Own-organization campaign activity, evidence submission, campaign drafts/review records, and expedition content management.</x:v>
+        <x:v>Own-organization portal access with owner/manager/contributor/viewer capabilities for campaigns, activities, evidence, and expeditions.</x:v>
       </x:c>
       <x:c r="F12" s="39" t="str">
-        <x:v>docs/user-guides/partner.md; src/app/partner/layout.tsx</x:v>
+        <x:v>docs/user-guides/partner.md; src/lib/partner-permissions.ts; src/lib/portal-actions.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3116,10 +3113,10 @@
         <x:v>/admin</x:v>
       </x:c>
       <x:c r="E13" s="55" t="str">
-        <x:v>Admin-only operations: campaigns, expeditions, partners, evidence verification, payments reconciliation, users, reports, audit. Can inspect partner portal.</x:v>
+        <x:v>Admin-only operations: campaigns, expeditions, partners, evidence verification, payment reconciliation, reports, audit, and full user/global/scoped role management.</x:v>
       </x:c>
       <x:c r="F13" s="45" t="str">
-        <x:v>docs/user-guides/admin.md; src/app/admin/layout.tsx; src/app/partner/layout.tsx</x:v>
+        <x:v>docs/user-guides/admin.md; src/app/admin/layout.tsx; src/lib/admin-user-actions.ts</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3457,6 +3454,83 @@
         <x:v>Schema inventory including roles, user_roles, organization_users, corporate_permissions, reports, evidence, and audit logs.</x:v>
       </x:c>
     </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>src/app/forbidden/page.tsx</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>Implementation</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Explicit forbidden page for unauthorized signed-in protected-route access.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>src/lib/corporate-access.ts</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>Implementation</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Shared corporate dashboard access guard for corporate workspace pages.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>src/lib/corporate-permissions.ts</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>Implementation</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Centralized corporate sub-role capability and employee-role assignment rules.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>src/lib/partner-permissions.ts</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>Implementation</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>Partner owner/manager/contributor/viewer capability mapping.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>src/lib/admin-user-actions.ts</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>Implementation</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Admin user management server actions for users, roles, sessions, partner membership, and corporate permissions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>src/lib/admin-user-management.ts</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>Implementation</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Admin user management role/status option and normalization helpers.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>tests/*permissions*.test.ts; tests/admin-user-management.test.ts; tests/account-destinations.test.ts</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>Test evidence</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Focused tests for partner permissions, corporate permissions, admin user role helpers, and forbidden redirects.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:C1"/>
